--- a/Ablation experiment.xlsx
+++ b/Ablation experiment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haochen/Documents/Development/bright-cmca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFCFA06-BC67-2940-AA30-BB2787F89B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412A03C6-0FC6-1945-982B-3ACEA97344C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20000" xr2:uid="{79C5FF15-FE7B-B844-917A-3EB10CF0BE82}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20000" firstSheet="1" activeTab="7" xr2:uid="{79C5FF15-FE7B-B844-917A-3EB10CF0BE82}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="7" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="SiamCRNN per-event" sheetId="10" r:id="rId10"/>
     <sheet name="DeepLabV3Plus" sheetId="11" r:id="rId11"/>
     <sheet name="DeepLabV3Plus per-event" sheetId="12" r:id="rId12"/>
+    <sheet name="ChangeMamba" sheetId="13" r:id="rId13"/>
+    <sheet name="ChangeMamba per-event" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="96">
   <si>
     <t>Method</t>
   </si>
@@ -278,6 +280,86 @@
   </si>
   <si>
     <t>DeepLabV3Plus + CMCA + CutMix 0.3</t>
+  </si>
+  <si>
+    <t>ChangeMamba</t>
+  </si>
+  <si>
+    <t>ChangeMamba + CutMix 0.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CutMix 0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA +CutMix 0.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA +CutMix 0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CutMix 0.25</t>
+  </si>
+  <si>
+    <t>ChangeMamba + CutMix 0.3</t>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA</t>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA + CutMix 0.25</t>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA + CutMix 0.3</t>
+  </si>
+  <si>
+    <t>+ CutMix 0.25</t>
+  </si>
+  <si>
+    <t>+ CutMix 0.3</t>
+  </si>
+  <si>
+    <t>+ CMCA</t>
+  </si>
+  <si>
+    <t>+ CMCA + CutMix 0.25</t>
+  </si>
+  <si>
+    <t>+ CMCA + CutMix 0.3</t>
+  </si>
+  <si>
+    <t>ChangeMamba</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA + CutMix 0.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeMamba + CMCA + CutMix 0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SiamAttnUNet + CMCA + CutMix 0.3</t>
+  </si>
+  <si>
+    <t>SiamAttnUNet + CMCA + CutMix 0.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SiamAttnUNet + CMCA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SiamAttnUNet + CMCA + CutMix 0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -335,18 +417,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -375,7 +451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -385,31 +461,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -418,19 +488,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,11 +1126,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F84AB9F-A280-504A-80C7-D2E7BDB8B4E9}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="34.5" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1093,874 +1164,1076 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>88.32</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>70.91</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>95.52</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>64.739999999999995</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>96.28</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>71.62</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="5">
         <v>37.479999999999997</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>53.59</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>88.65</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>70.180000000000007</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>95.54</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>64.44</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>96.28</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>72.36</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>36.270000000000003</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>52.84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>88.07</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>70.89</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>95.48</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>64.459999999999994</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>96.22</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>71.430000000000007</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>38.049999999999997</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>52.15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>88.68</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>72.650000000000006</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>95.59</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>65.39</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>96.29</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>72.790000000000006</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>39.299999999999997</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>53.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>89.09</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>72.03</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>95.82</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>66.069999999999993</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>96.52</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>73.290000000000006</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>40.53</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>53.93</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>89.18</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>72.430000000000007</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>95.81</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>66.16</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>96.5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>73.58</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>39.08</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>55.49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>89.88</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>72.61</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>96</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>66.84</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="7">
         <v>96.7</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="7">
         <v>74.62</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <v>39.97</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <v>56.06</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="8">
         <v>89.91</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <v>72.25</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>96.04</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>66.790000000000006</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="8">
         <v>96.75</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>74.680000000000007</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>39.03</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <v>56.7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>89.94</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>73.05</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>96.09</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>67.2</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>96.77</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>74.94</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <v>41.4</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <v>55.7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>89.9</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>71.959999999999994</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>95.97</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <v>66.55</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <v>96.72</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>74.349999999999994</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="7">
         <v>38.61</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <v>56.53</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>90</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="7">
         <v>72.39</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <v>96</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="7">
         <v>66.650000000000006</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="7">
         <v>96.74</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <v>74.62</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <v>39.49</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="7">
         <v>55.74</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>89.91</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <v>73.069999999999993</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>96</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>67.14</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
         <v>96.71</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="7">
         <v>74.540000000000006</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="7">
         <v>40.17</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>57.12</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>88.26</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>71.790000000000006</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>95.51</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>65.03</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>96.21</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>72.06</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>38.24</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>53.6</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>88.03</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>71.989999999999995</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>95.53</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>65.27</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>96.15</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>72</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <v>39.08</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>53.83</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>87.92</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>71.849999999999994</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>95.49</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>65.28</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>96.11</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>71.95</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>37.450000000000003</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>55.62</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>88.6</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>71.510000000000005</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>95.56</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>64.81</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>96.32</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>72.12</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <v>38.81</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>52.01</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>88.21</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>71.59</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>95.61</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>65.709999999999994</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <v>96.26</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <v>72.150000000000006</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <v>37.56</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="6">
         <v>56.86</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <v>88.77</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="6">
         <v>72.88</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>95.71</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="6">
         <v>66.260000000000005</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>96.39</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="6">
         <v>72.87</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>39.950000000000003</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>55.85</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="7">
         <v>89.11</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="7">
         <v>72.12</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="7">
         <v>95.83</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="7">
         <v>66.13</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="7">
         <v>96.49</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="7">
         <v>73.63</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
         <v>40.22</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="7">
         <v>54.17</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="7">
         <v>89.05</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>72.150000000000006</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="7">
         <v>95.85</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="7">
         <v>66.36</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="7">
         <v>96.49</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="7">
         <v>73.67</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="7">
         <v>39.200000000000003</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="7">
         <v>56.09</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>89.3</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="7">
         <v>72.290000000000006</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="9">
         <v>95.87</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="7">
         <v>66.33</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="9">
         <v>96.55</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="9">
         <v>73.790000000000006</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
         <v>39.619999999999997</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="7">
         <v>55.38</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>88.85</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>72.849999999999994</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>95.75</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>66.25</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="7">
         <v>96.42</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="7">
         <v>73.12</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="9">
         <v>41.26</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="7">
         <v>54.21</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>89.04</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="9">
         <v>73.13</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <v>95.75</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <v>66.52</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="7">
         <v>96.41</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="7">
         <v>73.489999999999995</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="7">
         <v>40.1</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="7">
         <v>56.06</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <v>89.15</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="7">
         <v>72.3</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="7">
         <v>95.82</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="7">
         <v>66.5</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="7">
         <v>96.49</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="7">
         <v>73.63</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="7">
         <v>39.07</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="9">
         <v>56.83</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>87.36</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>69.91</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>95.39</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
         <v>63.85</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>96.05</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="2">
         <v>70.819999999999993</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="2">
         <v>37.06</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="2">
         <v>51.45</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="2">
         <v>87.68</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="12">
         <v>71.77</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>95.53</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>65.25</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>96.1</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="2">
         <v>71.81</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="2">
         <v>53.3</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>86.59</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>68.239999999999995</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>95.37</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
         <v>63.46</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>95.93</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="2">
         <v>70.3</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="2">
         <v>37.56</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="2">
         <v>50.04</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="2">
         <v>87.71</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>69.760000000000005</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>95.56</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>64.83</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>96.23</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="2">
         <v>71.14</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="2">
         <v>38.18</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="2">
         <v>53.76</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="12">
         <v>88.79</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>71.22</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="12">
         <v>95.8</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="12">
         <v>65.790000000000006</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>96.44</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="12">
         <v>73.319999999999993</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="2">
         <v>39.26</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="12">
         <v>54.12</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="2">
         <v>88.45</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>70.87</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>95.72</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="2">
         <v>65.2</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>96.36</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="2">
         <v>72.89</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="12">
         <v>40.200000000000003</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="2">
         <v>51.35</v>
       </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="3">
+        <v>89.95</v>
+      </c>
+      <c r="C32" s="3">
+        <v>73.180000000000007</v>
+      </c>
+      <c r="D32" s="3">
+        <v>95.83</v>
+      </c>
+      <c r="E32" s="3">
+        <v>66.73</v>
+      </c>
+      <c r="F32" s="3">
+        <v>96.42</v>
+      </c>
+      <c r="G32" s="3">
+        <v>73.66</v>
+      </c>
+      <c r="H32" s="3">
+        <v>40.74</v>
+      </c>
+      <c r="I32" s="3">
+        <v>56.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="3">
+        <v>90.11</v>
+      </c>
+      <c r="C33" s="3">
+        <v>73.92</v>
+      </c>
+      <c r="D33" s="3">
+        <v>95.9</v>
+      </c>
+      <c r="E33" s="3">
+        <v>67</v>
+      </c>
+      <c r="F33" s="3">
+        <v>96.53</v>
+      </c>
+      <c r="G33" s="3">
+        <v>74.08</v>
+      </c>
+      <c r="H33" s="13">
+        <v>42.35</v>
+      </c>
+      <c r="I33" s="3">
+        <v>55.04</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="3">
+        <v>89.75</v>
+      </c>
+      <c r="C34" s="3">
+        <v>73.540000000000006</v>
+      </c>
+      <c r="D34" s="3">
+        <v>95.89</v>
+      </c>
+      <c r="E34" s="3">
+        <v>67.040000000000006</v>
+      </c>
+      <c r="F34" s="3">
+        <v>96.47</v>
+      </c>
+      <c r="G34" s="3">
+        <v>73.88</v>
+      </c>
+      <c r="H34" s="3">
+        <v>42.21</v>
+      </c>
+      <c r="I34" s="3">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="3">
+        <v>89.93</v>
+      </c>
+      <c r="C35" s="13">
+        <v>74.41</v>
+      </c>
+      <c r="D35" s="3">
+        <v>95.87</v>
+      </c>
+      <c r="E35" s="3">
+        <v>67.319999999999993</v>
+      </c>
+      <c r="F35" s="3">
+        <v>96.45</v>
+      </c>
+      <c r="G35" s="3">
+        <v>73.95</v>
+      </c>
+      <c r="H35" s="3">
+        <v>42.55</v>
+      </c>
+      <c r="I35" s="3">
+        <v>56.34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="3">
+        <v>89.79</v>
+      </c>
+      <c r="C36" s="3">
+        <v>66.25</v>
+      </c>
+      <c r="D36" s="3">
+        <v>95.72</v>
+      </c>
+      <c r="E36" s="3">
+        <v>63.7</v>
+      </c>
+      <c r="F36" s="3">
+        <v>96.49</v>
+      </c>
+      <c r="G36" s="3">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="H36" s="3">
+        <v>30.82</v>
+      </c>
+      <c r="I36" s="3">
+        <v>54.53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="13">
+        <v>90.12</v>
+      </c>
+      <c r="C37" s="3">
+        <v>74.31</v>
+      </c>
+      <c r="D37" s="13">
+        <v>95.92</v>
+      </c>
+      <c r="E37" s="13">
+        <v>67.430000000000007</v>
+      </c>
+      <c r="F37" s="13">
+        <v>96.54</v>
+      </c>
+      <c r="G37" s="13">
+        <v>74.12</v>
+      </c>
+      <c r="H37" s="3">
+        <v>41.82</v>
+      </c>
+      <c r="I37" s="13">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="Q47" s="1"/>
+    </row>
+    <row r="49" spans="11:18">
+      <c r="L49" s="1"/>
+    </row>
+    <row r="51" spans="11:18">
+      <c r="K51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="R51" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2668,22 +2941,22 @@
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>41.76</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>39.4</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>38.72</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>42.78</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>41.75</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="11">
         <v>45.26</v>
       </c>
       <c r="H2" t="s">
@@ -2694,22 +2967,22 @@
       <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>38.520000000000003</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>39.200000000000003</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>38.81</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <v>39.76</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>39.630000000000003</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="10">
         <v>38.99</v>
       </c>
       <c r="H3" t="s">
@@ -2720,22 +2993,22 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>58.79</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>61.49</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>59.38</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>61.71</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>60.14</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>57.16</v>
       </c>
       <c r="H4" t="s">
@@ -2746,22 +3019,22 @@
       <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>38.840000000000003</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>39.770000000000003</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>39.29</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>40.01</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <v>40.590000000000003</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>40.43</v>
       </c>
       <c r="H5" t="s">
@@ -2772,22 +3045,22 @@
       <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>61.98</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>65.260000000000005</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>61.44</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>63.7</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>63.9</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>63.15</v>
       </c>
       <c r="H6" t="s">
@@ -2798,22 +3071,22 @@
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>40.950000000000003</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>53.97</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="10">
         <v>49.33</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>45.88</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>48</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="10">
         <v>48.95</v>
       </c>
       <c r="H7" t="s">
@@ -2824,22 +3097,22 @@
       <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>43.8</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="10">
         <v>44.73</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="10">
         <v>44.86</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>43.62</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>44.93</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="11">
         <v>45.37</v>
       </c>
       <c r="H8" t="s">
@@ -2850,22 +3123,22 @@
       <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>49.41</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>50.16</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="10">
         <v>47.49</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>50.48</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <v>50.67</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="10">
         <v>49.74</v>
       </c>
       <c r="H9" t="s">
@@ -2876,22 +3149,22 @@
       <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>45.46</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>42.93</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="10">
         <v>42.09</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>40.119999999999997</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>40.11</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="10">
         <v>39.369999999999997</v>
       </c>
       <c r="H10" t="s">
@@ -2902,22 +3175,22 @@
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>55.86</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="10">
         <v>56.15</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="10">
         <v>54.39</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="10">
         <v>57.85</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <v>58.71</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="10">
         <v>57.17</v>
       </c>
       <c r="H11" t="s">
@@ -2928,22 +3201,22 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <v>42.33</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="10">
         <v>42.15</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="10">
         <v>41.46</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>42.35</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="11">
         <v>43.22</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="10">
         <v>43.07</v>
       </c>
       <c r="H12" t="s">
@@ -2954,22 +3227,22 @@
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <v>53.77</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="10">
         <v>56.58</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="10">
         <v>52.53</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="10">
         <v>53.92</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="11">
         <v>60.73</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="10">
         <v>57.28</v>
       </c>
       <c r="H13" t="s">
@@ -2980,22 +3253,22 @@
       <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <v>46.62</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>46.68</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>48.56</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>52.25</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>49.2</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="10">
         <v>49.14</v>
       </c>
       <c r="H14" t="s">
@@ -3006,22 +3279,22 @@
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
         <v>36.96</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <v>38.15</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="10">
         <v>37.54</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="10">
         <v>40.39</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <v>45.54</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="10">
         <v>40.81</v>
       </c>
       <c r="H15" t="s">
@@ -3032,26 +3305,680 @@
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>46.79</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="10">
         <v>48.33</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>46.85</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="10">
         <v>48.2</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="11">
         <v>49.08</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="10">
         <v>48.28</v>
       </c>
       <c r="H16" t="s">
         <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582E447A-4FB2-8648-859A-DC7228DC20E8}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="35.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>89.95</v>
+      </c>
+      <c r="C2">
+        <v>73.180000000000007</v>
+      </c>
+      <c r="D2">
+        <v>95.83</v>
+      </c>
+      <c r="E2">
+        <v>66.73</v>
+      </c>
+      <c r="F2">
+        <v>96.42</v>
+      </c>
+      <c r="G2">
+        <v>73.66</v>
+      </c>
+      <c r="H2">
+        <v>40.74</v>
+      </c>
+      <c r="I2">
+        <v>56.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3">
+        <v>90.11</v>
+      </c>
+      <c r="C3">
+        <v>73.92</v>
+      </c>
+      <c r="D3">
+        <v>95.9</v>
+      </c>
+      <c r="E3">
+        <v>67</v>
+      </c>
+      <c r="F3">
+        <v>96.53</v>
+      </c>
+      <c r="G3">
+        <v>74.08</v>
+      </c>
+      <c r="H3" s="1">
+        <v>42.35</v>
+      </c>
+      <c r="I3">
+        <v>55.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>89.75</v>
+      </c>
+      <c r="C4">
+        <v>73.540000000000006</v>
+      </c>
+      <c r="D4">
+        <v>95.89</v>
+      </c>
+      <c r="E4">
+        <v>67.040000000000006</v>
+      </c>
+      <c r="F4">
+        <v>96.47</v>
+      </c>
+      <c r="G4">
+        <v>73.88</v>
+      </c>
+      <c r="H4">
+        <v>42.21</v>
+      </c>
+      <c r="I4">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5">
+        <v>89.93</v>
+      </c>
+      <c r="C5" s="1">
+        <v>74.41</v>
+      </c>
+      <c r="D5">
+        <v>95.87</v>
+      </c>
+      <c r="E5">
+        <v>67.319999999999993</v>
+      </c>
+      <c r="F5">
+        <v>96.45</v>
+      </c>
+      <c r="G5">
+        <v>73.95</v>
+      </c>
+      <c r="H5">
+        <v>42.55</v>
+      </c>
+      <c r="I5">
+        <v>56.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6">
+        <v>89.79</v>
+      </c>
+      <c r="C6">
+        <v>66.25</v>
+      </c>
+      <c r="D6">
+        <v>95.72</v>
+      </c>
+      <c r="E6">
+        <v>63.7</v>
+      </c>
+      <c r="F6">
+        <v>96.49</v>
+      </c>
+      <c r="G6">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="H6">
+        <v>30.82</v>
+      </c>
+      <c r="I6">
+        <v>54.53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="1">
+        <v>90.12</v>
+      </c>
+      <c r="C7">
+        <v>74.31</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95.92</v>
+      </c>
+      <c r="E7" s="1">
+        <v>67.430000000000007</v>
+      </c>
+      <c r="F7" s="1">
+        <v>96.54</v>
+      </c>
+      <c r="G7" s="1">
+        <v>74.12</v>
+      </c>
+      <c r="H7">
+        <v>41.82</v>
+      </c>
+      <c r="I7" s="1">
+        <v>57.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A966389F-C01A-9F47-A6CC-43010D92D2EC}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="35.6640625" customWidth="1"/>
+    <col min="2" max="2" width="48.5" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" customWidth="1"/>
+    <col min="7" max="7" width="37" customWidth="1"/>
+    <col min="8" max="8" width="41.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>50.5</v>
+      </c>
+      <c r="C2">
+        <v>49.88</v>
+      </c>
+      <c r="D2">
+        <v>49.24</v>
+      </c>
+      <c r="E2" s="1">
+        <v>62.58</v>
+      </c>
+      <c r="F2">
+        <v>48.1</v>
+      </c>
+      <c r="G2">
+        <v>53.89</v>
+      </c>
+      <c r="H2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>39.44</v>
+      </c>
+      <c r="C3" s="1">
+        <v>39.94</v>
+      </c>
+      <c r="D3">
+        <v>39.24</v>
+      </c>
+      <c r="E3">
+        <v>39.58</v>
+      </c>
+      <c r="F3">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="G3">
+        <v>39.270000000000003</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>61.86</v>
+      </c>
+      <c r="C4">
+        <v>61.74</v>
+      </c>
+      <c r="D4">
+        <v>62.08</v>
+      </c>
+      <c r="E4">
+        <v>61.3</v>
+      </c>
+      <c r="F4">
+        <v>62.55</v>
+      </c>
+      <c r="G4">
+        <v>61.58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>41.24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>41.44</v>
+      </c>
+      <c r="D5">
+        <v>41.35</v>
+      </c>
+      <c r="E5">
+        <v>41.28</v>
+      </c>
+      <c r="F5">
+        <v>41.29</v>
+      </c>
+      <c r="G5">
+        <v>41.27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>63.75</v>
+      </c>
+      <c r="C6">
+        <v>64.55</v>
+      </c>
+      <c r="D6">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="E6" s="1">
+        <v>64.97</v>
+      </c>
+      <c r="F6">
+        <v>62.93</v>
+      </c>
+      <c r="G6">
+        <v>63.99</v>
+      </c>
+      <c r="H6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>51.14</v>
+      </c>
+      <c r="C7">
+        <v>55.25</v>
+      </c>
+      <c r="D7">
+        <v>50.49</v>
+      </c>
+      <c r="E7">
+        <v>51.95</v>
+      </c>
+      <c r="F7">
+        <v>55.85</v>
+      </c>
+      <c r="G7" s="1">
+        <v>57.8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>45.84</v>
+      </c>
+      <c r="C8">
+        <v>46.41</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="E8">
+        <v>45.65</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>46.65</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>53.34</v>
+      </c>
+      <c r="C9">
+        <v>50.77</v>
+      </c>
+      <c r="D9">
+        <v>53.83</v>
+      </c>
+      <c r="E9">
+        <v>52.15</v>
+      </c>
+      <c r="F9">
+        <v>49.79</v>
+      </c>
+      <c r="G9" s="1">
+        <v>54.56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>39.47</v>
+      </c>
+      <c r="C10">
+        <v>42.64</v>
+      </c>
+      <c r="D10">
+        <v>42.69</v>
+      </c>
+      <c r="E10">
+        <v>43.46</v>
+      </c>
+      <c r="F10">
+        <v>42.1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>44.65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>59.23</v>
+      </c>
+      <c r="C11">
+        <v>56.73</v>
+      </c>
+      <c r="D11">
+        <v>57.48</v>
+      </c>
+      <c r="E11" s="1">
+        <v>59.18</v>
+      </c>
+      <c r="F11">
+        <v>59.47</v>
+      </c>
+      <c r="G11">
+        <v>57.92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
+        <v>43.14</v>
+      </c>
+      <c r="C12">
+        <v>43.34</v>
+      </c>
+      <c r="D12">
+        <v>42.9</v>
+      </c>
+      <c r="E12">
+        <v>43.08</v>
+      </c>
+      <c r="F12">
+        <v>43.03</v>
+      </c>
+      <c r="G12" s="1">
+        <v>43.35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>63.29</v>
+      </c>
+      <c r="C13" s="1">
+        <v>68.959999999999994</v>
+      </c>
+      <c r="D13">
+        <v>64.03</v>
+      </c>
+      <c r="E13">
+        <v>67.08</v>
+      </c>
+      <c r="F13">
+        <v>51.29</v>
+      </c>
+      <c r="G13">
+        <v>67.760000000000005</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>53.91</v>
+      </c>
+      <c r="C14">
+        <v>53.9</v>
+      </c>
+      <c r="D14">
+        <v>49.88</v>
+      </c>
+      <c r="E14">
+        <v>51.66</v>
+      </c>
+      <c r="F14" s="1">
+        <v>54.75</v>
+      </c>
+      <c r="G14">
+        <v>52.28</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>39.380000000000003</v>
+      </c>
+      <c r="C15">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="D15">
+        <v>38.75</v>
+      </c>
+      <c r="E15">
+        <v>37.83</v>
+      </c>
+      <c r="F15">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="G15" s="1">
+        <v>40.49</v>
+      </c>
+      <c r="H15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>50.39</v>
+      </c>
+      <c r="C16">
+        <v>51.03</v>
+      </c>
+      <c r="D16">
+        <v>50.25</v>
+      </c>
+      <c r="E16">
+        <v>51.55</v>
+      </c>
+      <c r="F16">
+        <v>49.54</v>
+      </c>
+      <c r="G16" s="1">
+        <v>51.82</v>
+      </c>
+      <c r="H16" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3062,7 +3989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C88A506-B9C6-3C4B-83B4-0C808C065E7F}">
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.1640625" customWidth="1"/>
@@ -3096,1526 +4023,1820 @@
     <col min="29" max="29" width="36.83203125" customWidth="1"/>
     <col min="30" max="30" width="45" customWidth="1"/>
     <col min="31" max="31" width="43.33203125" customWidth="1"/>
+    <col min="32" max="32" width="29.6640625" customWidth="1"/>
+    <col min="33" max="33" width="31.1640625" customWidth="1"/>
+    <col min="34" max="34" width="48.83203125" customWidth="1"/>
+    <col min="35" max="35" width="33.83203125" customWidth="1"/>
+    <col min="36" max="36" width="30.1640625" customWidth="1"/>
+    <col min="37" max="37" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="W1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="X1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Y1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AD1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AE1" s="16" t="s">
+      <c r="AE1" s="14" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG1" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH1" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI1" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ1" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK1" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>48.01</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>49.34</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>49.79</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="2">
         <v>52.12</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>54.94</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="12">
         <v>64.069999999999993</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="3">
         <v>52.77</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="13">
         <v>54.63</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="3">
         <v>49.43</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="3">
         <v>51.46</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="3">
         <v>52.01</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>48.69</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="2">
         <v>56.81</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="2">
         <v>48.12</v>
       </c>
-      <c r="P2" s="14">
+      <c r="P2" s="12">
         <v>59.15</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="2">
         <v>45.78</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="2">
         <v>48</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>52.73</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="3">
         <v>48.07</v>
       </c>
-      <c r="U2" s="15">
+      <c r="U2" s="13">
         <v>48.11</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="3">
         <v>43.18</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="3">
         <v>45.48</v>
       </c>
-      <c r="X2" s="5">
+      <c r="X2" s="3">
         <v>47.78</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="3">
         <v>41.28</v>
       </c>
-      <c r="Z2" s="17">
+      <c r="Z2" s="15">
         <v>41.76</v>
       </c>
-      <c r="AA2" s="17">
+      <c r="AA2" s="15">
         <v>39.4</v>
       </c>
-      <c r="AB2" s="17">
+      <c r="AB2" s="15">
         <v>38.72</v>
       </c>
-      <c r="AC2" s="17">
+      <c r="AC2" s="15">
         <v>42.78</v>
       </c>
-      <c r="AD2" s="17">
+      <c r="AD2" s="15">
         <v>41.75</v>
       </c>
-      <c r="AE2" s="18">
+      <c r="AE2" s="16">
         <v>45.26</v>
       </c>
-    </row>
-    <row r="3" spans="1:31">
+      <c r="AF2" s="3">
+        <v>50.5</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>49.88</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>49.24</v>
+      </c>
+      <c r="AI2" s="13">
+        <v>62.58</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>48.1</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>53.89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="12">
         <v>39.619999999999997</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>39.119999999999997</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>38.880000000000003</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>39.479999999999997</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>41.12</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>39.54</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="3">
         <v>39.82</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="3">
         <v>41.14</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="3">
         <v>40.340000000000003</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="3">
         <v>40.76</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="13">
         <v>41.3</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="3">
         <v>39.97</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="2">
         <v>39.61</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="2">
         <v>39</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="2">
         <v>39.08</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="12">
         <v>39.659999999999997</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="2">
         <v>38.99</v>
       </c>
-      <c r="S3" s="4">
+      <c r="S3" s="2">
         <v>39.25</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T3" s="3">
         <v>40.08</v>
       </c>
-      <c r="U3" s="5">
+      <c r="U3" s="3">
         <v>40.19</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="3">
         <v>41.53</v>
       </c>
-      <c r="W3" s="15">
+      <c r="W3" s="13">
         <v>47.79</v>
       </c>
-      <c r="X3" s="5">
+      <c r="X3" s="3">
         <v>40.380000000000003</v>
       </c>
-      <c r="Y3" s="5">
+      <c r="Y3" s="3">
         <v>39.97</v>
       </c>
-      <c r="Z3" s="17">
+      <c r="Z3" s="15">
         <v>38.520000000000003</v>
       </c>
-      <c r="AA3" s="17">
+      <c r="AA3" s="15">
         <v>39.200000000000003</v>
       </c>
-      <c r="AB3" s="17">
+      <c r="AB3" s="15">
         <v>38.81</v>
       </c>
-      <c r="AC3" s="18">
+      <c r="AC3" s="16">
         <v>39.76</v>
       </c>
-      <c r="AD3" s="17">
+      <c r="AD3" s="15">
         <v>39.630000000000003</v>
       </c>
-      <c r="AE3" s="17">
+      <c r="AE3" s="15">
         <v>38.99</v>
       </c>
-    </row>
-    <row r="4" spans="1:31">
+      <c r="AF3" s="3">
+        <v>39.44</v>
+      </c>
+      <c r="AG3" s="13">
+        <v>39.94</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>39.24</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>39.58</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>39.270000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>61.58</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>61.88</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>61.25</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>61.19</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>61.78</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="12">
         <v>62.99</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>62.06</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>62.03</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="3">
         <v>60.6</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="13">
         <v>62.48</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="3">
         <v>61.44</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="3">
         <v>61.43</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="2">
         <v>61.38</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="2">
         <v>61.34</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="2">
         <v>60.81</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="2">
         <v>60.95</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="2">
         <v>61.06</v>
       </c>
-      <c r="S4" s="4">
+      <c r="S4" s="2">
         <v>60.93</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="3">
         <v>59.83</v>
       </c>
-      <c r="U4" s="15">
+      <c r="U4" s="13">
         <v>61.8</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="3">
         <v>61.5</v>
       </c>
-      <c r="W4" s="5">
+      <c r="W4" s="3">
         <v>60.29</v>
       </c>
-      <c r="X4" s="5">
+      <c r="X4" s="3">
         <v>61.28</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="Y4" s="3">
         <v>60.83</v>
       </c>
-      <c r="Z4" s="17">
+      <c r="Z4" s="15">
         <v>58.79</v>
       </c>
-      <c r="AA4" s="17">
+      <c r="AA4" s="15">
         <v>61.49</v>
       </c>
-      <c r="AB4" s="17">
+      <c r="AB4" s="15">
         <v>59.38</v>
       </c>
-      <c r="AC4" s="18">
+      <c r="AC4" s="16">
         <v>61.71</v>
       </c>
-      <c r="AD4" s="17">
+      <c r="AD4" s="15">
         <v>60.14</v>
       </c>
-      <c r="AE4" s="17">
+      <c r="AE4" s="15">
         <v>57.16</v>
       </c>
-    </row>
-    <row r="5" spans="1:31">
+      <c r="AF4" s="3">
+        <v>61.86</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>61.74</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>62.08</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>61.3</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>62.55</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>61.58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
       <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>41.04</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>41.33</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>40.92</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>41.29</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>41.43</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="12">
         <v>41.74</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="13">
         <v>42.1</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="3">
         <v>42.02</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="3">
         <v>41.76</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="3">
         <v>42.03</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="3">
         <v>42.08</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="3">
         <v>41.87</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="2">
         <v>40.17</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="2">
         <v>40.71</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="2">
         <v>40.770000000000003</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="12">
         <v>41.41</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="2">
         <v>40.86</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S5" s="2">
         <v>40.659999999999997</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="3">
         <v>41.37</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="3">
         <v>41.35</v>
       </c>
-      <c r="V5" s="15">
+      <c r="V5" s="13">
         <v>41.55</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="3">
         <v>41.1</v>
       </c>
-      <c r="X5" s="5">
+      <c r="X5" s="3">
         <v>41.37</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="Y5" s="3">
         <v>41.32</v>
       </c>
-      <c r="Z5" s="17">
+      <c r="Z5" s="15">
         <v>38.840000000000003</v>
       </c>
-      <c r="AA5" s="17">
+      <c r="AA5" s="15">
         <v>39.770000000000003</v>
       </c>
-      <c r="AB5" s="17">
+      <c r="AB5" s="15">
         <v>39.29</v>
       </c>
-      <c r="AC5" s="17">
+      <c r="AC5" s="15">
         <v>40.01</v>
       </c>
-      <c r="AD5" s="18">
+      <c r="AD5" s="16">
         <v>40.590000000000003</v>
       </c>
-      <c r="AE5" s="17">
+      <c r="AE5" s="15">
         <v>40.43</v>
       </c>
-    </row>
-    <row r="6" spans="1:31">
+      <c r="AF5" s="3">
+        <v>41.24</v>
+      </c>
+      <c r="AG5" s="13">
+        <v>41.44</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>41.28</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>41.29</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>41.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
       <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>62.25</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>62.22</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>62.1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>62.21</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>62.54</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <v>63.01</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="3">
         <v>63.57</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="3">
         <v>65.03</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="3">
         <v>64.61</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="3">
         <v>64.39</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="13">
         <v>65.14</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="3">
         <v>64.95</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="2">
         <v>64.8</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="2">
         <v>62.84</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="12">
         <v>66.8</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="2">
         <v>62.92</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="2">
         <v>64.930000000000007</v>
       </c>
-      <c r="S6" s="4">
+      <c r="S6" s="2">
         <v>64.040000000000006</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="3">
         <v>63.46</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="3">
         <v>63.71</v>
       </c>
-      <c r="V6" s="5">
+      <c r="V6" s="3">
         <v>63.2</v>
       </c>
-      <c r="W6" s="5">
+      <c r="W6" s="3">
         <v>62.84</v>
       </c>
-      <c r="X6" s="5">
+      <c r="X6" s="3">
         <v>64.239999999999995</v>
       </c>
-      <c r="Y6" s="15">
+      <c r="Y6" s="13">
         <v>68.87</v>
       </c>
-      <c r="Z6" s="17">
+      <c r="Z6" s="15">
         <v>61.98</v>
       </c>
-      <c r="AA6" s="18">
+      <c r="AA6" s="16">
         <v>65.260000000000005</v>
       </c>
-      <c r="AB6" s="17">
+      <c r="AB6" s="15">
         <v>61.44</v>
       </c>
-      <c r="AC6" s="17">
+      <c r="AC6" s="15">
         <v>63.7</v>
       </c>
-      <c r="AD6" s="17">
+      <c r="AD6" s="15">
         <v>63.9</v>
       </c>
-      <c r="AE6" s="17">
+      <c r="AE6" s="15">
         <v>63.15</v>
       </c>
-    </row>
-    <row r="7" spans="1:31">
+      <c r="AF6" s="3">
+        <v>63.75</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>64.55</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="AI6" s="13">
+        <v>64.97</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>62.93</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>63.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>50.96</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>53.57</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>52.76</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>53.36</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>53.92</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="12">
         <v>57.56</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="3">
         <v>57.72</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <v>59.02</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="3">
         <v>58.46</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="3">
         <v>57.62</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="3">
         <v>58.85</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="3">
         <v>56.4</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="2">
         <v>45.66</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="2">
         <v>50.67</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="2">
         <v>49.56</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="2">
         <v>52.68</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="12">
         <v>53.18</v>
       </c>
-      <c r="S7" s="4">
+      <c r="S7" s="2">
         <v>51.53</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="3">
         <v>55.58</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="3">
         <v>57.4</v>
       </c>
-      <c r="V7" s="15">
+      <c r="V7" s="13">
         <v>57.44</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="3">
         <v>53.98</v>
       </c>
-      <c r="X7" s="5">
+      <c r="X7" s="3">
         <v>57</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="3">
         <v>56.68</v>
       </c>
-      <c r="Z7" s="17">
+      <c r="Z7" s="15">
         <v>40.950000000000003</v>
       </c>
-      <c r="AA7" s="18">
+      <c r="AA7" s="16">
         <v>53.97</v>
       </c>
-      <c r="AB7" s="17">
+      <c r="AB7" s="15">
         <v>49.33</v>
       </c>
-      <c r="AC7" s="17">
+      <c r="AC7" s="15">
         <v>45.88</v>
       </c>
-      <c r="AD7" s="17">
+      <c r="AD7" s="15">
         <v>48</v>
       </c>
-      <c r="AE7" s="17">
+      <c r="AE7" s="15">
         <v>48.95</v>
       </c>
-    </row>
-    <row r="8" spans="1:31">
+      <c r="AF7" s="3">
+        <v>51.14</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>55.25</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>50.49</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>51.95</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>55.85</v>
+      </c>
+      <c r="AK7" s="13">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
       <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>44.69</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>45.45</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>43.12</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>46.28</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>46.22</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <v>46.56</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="3">
         <v>47.42</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="3">
         <v>47.2</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="3">
         <v>46.88</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="13">
         <v>47.87</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="3">
         <v>45.73</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="3">
         <v>46.6</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="2">
         <v>43.94</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="2">
         <v>44.85</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
         <v>43.63</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="2">
         <v>44.59</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R8" s="2">
         <v>45</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="12">
         <v>45.02</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="3">
         <v>46.74</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="3">
         <v>45.98</v>
       </c>
-      <c r="V8" s="15">
+      <c r="V8" s="13">
         <v>46.77</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="3">
         <v>45.87</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8" s="3">
         <v>46.31</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="Y8" s="3">
         <v>46.65</v>
       </c>
-      <c r="Z8" s="17">
+      <c r="Z8" s="15">
         <v>43.8</v>
       </c>
-      <c r="AA8" s="17">
+      <c r="AA8" s="15">
         <v>44.73</v>
       </c>
-      <c r="AB8" s="17">
+      <c r="AB8" s="15">
         <v>44.86</v>
       </c>
-      <c r="AC8" s="17">
+      <c r="AC8" s="15">
         <v>43.62</v>
       </c>
-      <c r="AD8" s="17">
+      <c r="AD8" s="15">
         <v>44.93</v>
       </c>
-      <c r="AE8" s="18">
+      <c r="AE8" s="16">
         <v>45.37</v>
       </c>
-    </row>
-    <row r="9" spans="1:31">
+      <c r="AF8" s="3">
+        <v>45.84</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>46.41</v>
+      </c>
+      <c r="AH8" s="13">
+        <v>46.9</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>45.65</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>44</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>46.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>49.11</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>49.55</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>50.19</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>52.03</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>53.81</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="2">
         <v>51.49</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="3">
         <v>51.31</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="3">
         <v>51.98</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="3">
         <v>51.9</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="13">
         <v>52.51</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="3">
         <v>50.22</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="3">
         <v>51.69</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="2">
         <v>48.91</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="2">
         <v>47.94</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="2">
         <v>49.04</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="2">
         <v>46.97</v>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="12">
         <v>49.74</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="2">
         <v>48.25</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="3">
         <v>52.98</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="3">
         <v>52.14</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="3">
         <v>53.23</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="3">
         <v>50.81</v>
       </c>
-      <c r="X9" s="15">
+      <c r="X9" s="13">
         <v>53.3</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="3">
         <v>51.9</v>
       </c>
-      <c r="Z9" s="17">
+      <c r="Z9" s="15">
         <v>49.41</v>
       </c>
-      <c r="AA9" s="17">
+      <c r="AA9" s="15">
         <v>50.16</v>
       </c>
-      <c r="AB9" s="17">
+      <c r="AB9" s="15">
         <v>47.49</v>
       </c>
-      <c r="AC9" s="17">
+      <c r="AC9" s="15">
         <v>50.48</v>
       </c>
-      <c r="AD9" s="18">
+      <c r="AD9" s="16">
         <v>50.67</v>
       </c>
-      <c r="AE9" s="17">
+      <c r="AE9" s="15">
         <v>49.74</v>
       </c>
-    </row>
-    <row r="10" spans="1:31">
+      <c r="AF9" s="3">
+        <v>53.34</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>50.77</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>53.83</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>52.15</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>49.79</v>
+      </c>
+      <c r="AK9" s="13">
+        <v>54.56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>39.46</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>40.08</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>41.48</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>41.87</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>42.57</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="12">
         <v>45.56</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="3">
         <v>45.9</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="3">
         <v>45.09</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="3">
         <v>46.15</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="3">
         <v>45.19</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="13">
         <v>49.29</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="3">
         <v>48.2</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="2">
         <v>38.770000000000003</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="2">
         <v>40.33</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="2">
         <v>38.08</v>
       </c>
-      <c r="Q10" s="14">
+      <c r="Q10" s="12">
         <v>40.83</v>
       </c>
-      <c r="R10" s="4">
+      <c r="R10" s="2">
         <v>38.659999999999997</v>
       </c>
-      <c r="S10" s="4">
+      <c r="S10" s="2">
         <v>40.130000000000003</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="3">
         <v>43.16</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10" s="3">
         <v>42.07</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10" s="3">
         <v>43.21</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="3">
         <v>43.92</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X10" s="3">
         <v>42.4</v>
       </c>
-      <c r="Y10" s="15">
+      <c r="Y10" s="13">
         <v>45.75</v>
       </c>
-      <c r="Z10" s="18">
+      <c r="Z10" s="16">
         <v>45.46</v>
       </c>
-      <c r="AA10" s="17">
+      <c r="AA10" s="15">
         <v>42.93</v>
       </c>
-      <c r="AB10" s="17">
+      <c r="AB10" s="15">
         <v>42.09</v>
       </c>
-      <c r="AC10" s="17">
+      <c r="AC10" s="15">
         <v>40.119999999999997</v>
       </c>
-      <c r="AD10" s="17">
+      <c r="AD10" s="15">
         <v>40.11</v>
       </c>
-      <c r="AE10" s="17">
+      <c r="AE10" s="15">
         <v>39.369999999999997</v>
       </c>
-    </row>
-    <row r="11" spans="1:31">
+      <c r="AF10" s="3">
+        <v>39.47</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>42.64</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>42.69</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>43.46</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>42.1</v>
+      </c>
+      <c r="AK10" s="13">
+        <v>44.65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>55.61</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>56.73</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>55.25</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>56.86</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>57.96</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="12">
         <v>58.32</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="3">
         <v>59.85</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="3">
         <v>59.59</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="3">
         <v>60.57</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="13">
         <v>61.08</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="3">
         <v>60.03</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="3">
         <v>60.94</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="2">
         <v>47.2</v>
       </c>
-      <c r="O11" s="4">
+      <c r="O11" s="2">
         <v>57.08</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="12">
         <v>60.31</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="Q11" s="2">
         <v>56.52</v>
       </c>
-      <c r="R11" s="4">
+      <c r="R11" s="2">
         <v>56.85</v>
       </c>
-      <c r="S11" s="4">
+      <c r="S11" s="2">
         <v>54.99</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="13">
         <v>60.61</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11" s="3">
         <v>58.09</v>
       </c>
-      <c r="V11" s="5">
+      <c r="V11" s="3">
         <v>59.39</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="3">
         <v>57.51</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="3">
         <v>60.34</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="Y11" s="3">
         <v>58.28</v>
       </c>
-      <c r="Z11" s="17">
+      <c r="Z11" s="15">
         <v>55.86</v>
       </c>
-      <c r="AA11" s="17">
+      <c r="AA11" s="15">
         <v>56.15</v>
       </c>
-      <c r="AB11" s="17">
+      <c r="AB11" s="15">
         <v>54.39</v>
       </c>
-      <c r="AC11" s="17">
+      <c r="AC11" s="15">
         <v>57.85</v>
       </c>
-      <c r="AD11" s="18">
+      <c r="AD11" s="16">
         <v>58.71</v>
       </c>
-      <c r="AE11" s="17">
+      <c r="AE11" s="15">
         <v>57.17</v>
       </c>
-    </row>
-    <row r="12" spans="1:31">
+      <c r="AF11" s="3">
+        <v>59.23</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>56.73</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>57.48</v>
+      </c>
+      <c r="AI11" s="13">
+        <v>59.18</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>59.47</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>57.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>42.61</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>43.05</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>42.49</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>42.82</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>43.4</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="12">
         <v>43.59</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="13">
         <v>45.87</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="3">
         <v>43.97</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="3">
         <v>44.14</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="3">
         <v>44</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="3">
         <v>44.04</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="3">
         <v>44.14</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="2">
         <v>42.98</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="2">
         <v>42.94</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="2">
         <v>42.75</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="2">
         <v>42.91</v>
       </c>
-      <c r="R12" s="14">
+      <c r="R12" s="12">
         <v>43.32</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S12" s="2">
         <v>43.06</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="13">
         <v>43.36</v>
       </c>
-      <c r="U12" s="5">
+      <c r="U12" s="3">
         <v>43.31</v>
       </c>
-      <c r="V12" s="5">
+      <c r="V12" s="3">
         <v>43.27</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W12" s="3">
         <v>43.24</v>
       </c>
-      <c r="X12" s="5">
+      <c r="X12" s="3">
         <v>42.81</v>
       </c>
-      <c r="Y12" s="5">
+      <c r="Y12" s="3">
         <v>43.25</v>
       </c>
-      <c r="Z12" s="17">
+      <c r="Z12" s="15">
         <v>42.33</v>
       </c>
-      <c r="AA12" s="17">
+      <c r="AA12" s="15">
         <v>42.15</v>
       </c>
-      <c r="AB12" s="17">
+      <c r="AB12" s="15">
         <v>41.46</v>
       </c>
-      <c r="AC12" s="17">
+      <c r="AC12" s="15">
         <v>42.35</v>
       </c>
-      <c r="AD12" s="18">
+      <c r="AD12" s="16">
         <v>43.22</v>
       </c>
-      <c r="AE12" s="17">
+      <c r="AE12" s="15">
         <v>43.07</v>
       </c>
-    </row>
-    <row r="13" spans="1:31">
+      <c r="AF12" s="3">
+        <v>43.14</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>43.34</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>43.08</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>43.03</v>
+      </c>
+      <c r="AK12" s="13">
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
       <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>53.31</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>53.16</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <v>60.34</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
         <v>56.94</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>66.069999999999993</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="2">
         <v>62.74</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="3">
         <v>62.8</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="3">
         <v>58.15</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="3">
         <v>63.65</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="3">
         <v>57.57</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="3">
         <v>62.1</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="13">
         <v>64.66</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="2">
         <v>62.23</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="2">
         <v>63.36</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="2">
         <v>63.88</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="2">
         <v>57.62</v>
       </c>
-      <c r="R13" s="4">
+      <c r="R13" s="2">
         <v>59.57</v>
       </c>
-      <c r="S13" s="14">
+      <c r="S13" s="12">
         <v>64.680000000000007</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="3">
         <v>57.22</v>
       </c>
-      <c r="U13" s="5">
+      <c r="U13" s="3">
         <v>62.63</v>
       </c>
-      <c r="V13" s="5">
+      <c r="V13" s="3">
         <v>58.86</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="3">
         <v>60.4</v>
       </c>
-      <c r="X13" s="15">
+      <c r="X13" s="13">
         <v>62.97</v>
       </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="3">
         <v>62.24</v>
       </c>
-      <c r="Z13" s="17">
+      <c r="Z13" s="15">
         <v>53.77</v>
       </c>
-      <c r="AA13" s="17">
+      <c r="AA13" s="15">
         <v>56.58</v>
       </c>
-      <c r="AB13" s="17">
+      <c r="AB13" s="15">
         <v>52.53</v>
       </c>
-      <c r="AC13" s="17">
+      <c r="AC13" s="15">
         <v>53.92</v>
       </c>
-      <c r="AD13" s="18">
+      <c r="AD13" s="16">
         <v>60.73</v>
       </c>
-      <c r="AE13" s="17">
+      <c r="AE13" s="15">
         <v>57.28</v>
       </c>
-    </row>
-    <row r="14" spans="1:31">
+      <c r="AF13" s="3">
+        <v>63.29</v>
+      </c>
+      <c r="AG13" s="13">
+        <v>68.959999999999994</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>64.03</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>67.08</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>51.29</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>67.760000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
       <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>46.67</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>47.15</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>41.74</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
         <v>39.51</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>51.55</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="2">
         <v>47.03</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="3">
         <v>53.95</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="3">
         <v>54.61</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="3">
         <v>52.22</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="3">
         <v>53.04</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="13">
         <v>54.87</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="3">
         <v>54.69</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="2">
         <v>42.37</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="2">
         <v>44.42</v>
       </c>
-      <c r="P14" s="14">
+      <c r="P14" s="12">
         <v>53.15</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="2">
         <v>42.91</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R14" s="2">
         <v>46.08</v>
       </c>
-      <c r="S14" s="4">
+      <c r="S14" s="2">
         <v>50.97</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="3">
         <v>53.47</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14" s="3">
         <v>52.17</v>
       </c>
-      <c r="V14" s="15">
+      <c r="V14" s="13">
         <v>54.69</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="3">
         <v>53.13</v>
       </c>
-      <c r="X14" s="5">
+      <c r="X14" s="3">
         <v>52.96</v>
       </c>
-      <c r="Y14" s="5">
+      <c r="Y14" s="3">
         <v>51.87</v>
       </c>
-      <c r="Z14" s="17">
+      <c r="Z14" s="15">
         <v>46.62</v>
       </c>
-      <c r="AA14" s="17">
+      <c r="AA14" s="15">
         <v>46.68</v>
       </c>
-      <c r="AB14" s="17">
+      <c r="AB14" s="15">
         <v>48.56</v>
       </c>
-      <c r="AC14" s="18">
+      <c r="AC14" s="16">
         <v>52.25</v>
       </c>
-      <c r="AD14" s="17">
+      <c r="AD14" s="15">
         <v>49.2</v>
       </c>
-      <c r="AE14" s="17">
+      <c r="AE14" s="15">
         <v>49.14</v>
       </c>
-    </row>
-    <row r="15" spans="1:31">
+      <c r="AF14" s="3">
+        <v>53.91</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>53.9</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>49.88</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>51.66</v>
+      </c>
+      <c r="AJ14" s="13">
+        <v>54.75</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>52.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>38.35</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>37.479999999999997</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>36.39</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>42.14</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>37.950000000000003</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="2">
         <v>38.049999999999997</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="3">
         <v>43.38</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="3">
         <v>43.78</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="3">
         <v>42.8</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="13">
         <v>46.95</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="3">
         <v>39.299999999999997</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="3">
         <v>39.020000000000003</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="12">
         <v>44.04</v>
       </c>
-      <c r="O15" s="4">
+      <c r="O15" s="2">
         <v>37.79</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="2">
         <v>36.979999999999997</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="Q15" s="2">
         <v>39.5</v>
       </c>
-      <c r="R15" s="4">
+      <c r="R15" s="2">
         <v>38.51</v>
       </c>
-      <c r="S15" s="4">
+      <c r="S15" s="2">
         <v>37.78</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="3">
         <v>38.08</v>
       </c>
-      <c r="U15" s="5">
+      <c r="U15" s="3">
         <v>39.42</v>
       </c>
-      <c r="V15" s="5">
+      <c r="V15" s="3">
         <v>38.96</v>
       </c>
-      <c r="W15" s="5">
+      <c r="W15" s="3">
         <v>40.85</v>
       </c>
-      <c r="X15" s="15">
+      <c r="X15" s="13">
         <v>42.36</v>
       </c>
-      <c r="Y15" s="5">
+      <c r="Y15" s="3">
         <v>41.34</v>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="15">
         <v>36.96</v>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="15">
         <v>38.15</v>
       </c>
-      <c r="AB15" s="17">
+      <c r="AB15" s="15">
         <v>37.54</v>
       </c>
-      <c r="AC15" s="17">
+      <c r="AC15" s="15">
         <v>40.39</v>
       </c>
-      <c r="AD15" s="18">
+      <c r="AD15" s="16">
         <v>45.54</v>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="15">
         <v>40.81</v>
       </c>
-    </row>
-    <row r="16" spans="1:31">
+      <c r="AF15" s="3">
+        <v>39.380000000000003</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>38.75</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>37.83</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="AK15" s="13">
+        <v>40.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>48.09</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>48.58</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>48.33</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>49.15</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>51.09</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="12">
         <v>51.59</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="13">
         <v>52.04</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="3">
         <v>52.02</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="3">
         <v>51.68</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="3">
         <v>51.92</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="3">
         <v>51.88</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="3">
         <v>51.66</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="2">
         <v>48.49</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O16" s="2">
         <v>48.67</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="2">
         <v>50.29</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="2">
         <v>48.23</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R16" s="2">
         <v>48.91</v>
       </c>
-      <c r="S16" s="14">
+      <c r="S16" s="12">
         <v>49.57</v>
       </c>
-      <c r="T16" s="5">
+      <c r="T16" s="3">
         <v>50.29</v>
       </c>
-      <c r="U16" s="5">
+      <c r="U16" s="3">
         <v>50.6</v>
       </c>
-      <c r="V16" s="5">
+      <c r="V16" s="3">
         <v>50.48</v>
       </c>
-      <c r="W16" s="5">
+      <c r="W16" s="3">
         <v>50.52</v>
       </c>
-      <c r="X16" s="15">
+      <c r="X16" s="13">
         <v>51.11</v>
       </c>
-      <c r="Y16" s="5">
+      <c r="Y16" s="3">
         <v>50.73</v>
       </c>
-      <c r="Z16" s="17">
+      <c r="Z16" s="15">
         <v>46.79</v>
       </c>
-      <c r="AA16" s="17">
+      <c r="AA16" s="15">
         <v>48.33</v>
       </c>
-      <c r="AB16" s="17">
+      <c r="AB16" s="15">
         <v>46.85</v>
       </c>
-      <c r="AC16" s="17">
+      <c r="AC16" s="15">
         <v>48.2</v>
       </c>
-      <c r="AD16" s="18">
+      <c r="AD16" s="16">
         <v>49.08</v>
       </c>
-      <c r="AE16" s="17">
+      <c r="AE16" s="15">
         <v>48.28</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>50.39</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>51.03</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>50.25</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>51.55</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>49.54</v>
+      </c>
+      <c r="AK16" s="13">
+        <v>51.82</v>
       </c>
     </row>
     <row r="27" spans="2:25">
@@ -6093,86 +7314,86 @@
         <v>38</v>
       </c>
       <c r="B5">
-        <v>88.6</v>
+        <v>88.08</v>
       </c>
       <c r="C5">
-        <v>71.510000000000005</v>
+        <v>72.150000000000006</v>
       </c>
       <c r="D5">
-        <v>95.56</v>
+        <v>95.49</v>
       </c>
       <c r="E5">
-        <v>64.81</v>
+        <v>65.05</v>
       </c>
       <c r="F5">
-        <v>96.32</v>
+        <v>96.19</v>
       </c>
       <c r="G5">
-        <v>72.12</v>
+        <v>71.67</v>
       </c>
       <c r="H5">
-        <v>38.81</v>
+        <v>39.5</v>
       </c>
       <c r="I5">
-        <v>52.01</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="B6">
-        <v>88.21</v>
-      </c>
-      <c r="C6">
-        <v>71.59</v>
-      </c>
-      <c r="D6">
-        <v>95.61</v>
-      </c>
-      <c r="E6">
-        <v>65.709999999999994</v>
-      </c>
-      <c r="F6">
-        <v>96.26</v>
-      </c>
-      <c r="G6">
-        <v>72.150000000000006</v>
+      <c r="B6" s="1">
+        <v>88.44</v>
+      </c>
+      <c r="C6" s="1">
+        <v>72.67</v>
+      </c>
+      <c r="D6" s="1">
+        <v>95.67</v>
+      </c>
+      <c r="E6" s="1">
+        <v>66.28</v>
+      </c>
+      <c r="F6" s="1">
+        <v>96.33</v>
+      </c>
+      <c r="G6" s="1">
+        <v>72.55</v>
       </c>
       <c r="H6">
-        <v>37.56</v>
+        <v>38.94</v>
       </c>
       <c r="I6" s="1">
-        <v>56.86</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3">
-        <v>88.77</v>
-      </c>
-      <c r="C7" s="3">
-        <v>72.88</v>
-      </c>
-      <c r="D7" s="3">
-        <v>95.71</v>
-      </c>
-      <c r="E7" s="3">
-        <v>66.260000000000005</v>
-      </c>
-      <c r="F7" s="3">
-        <v>96.39</v>
-      </c>
-      <c r="G7" s="3">
-        <v>72.87</v>
-      </c>
-      <c r="H7" s="3">
-        <v>39.950000000000003</v>
-      </c>
-      <c r="I7" s="2">
-        <v>55.85</v>
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7">
+        <v>88.35</v>
+      </c>
+      <c r="C7">
+        <v>71.25</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95.67</v>
+      </c>
+      <c r="E7">
+        <v>65.78</v>
+      </c>
+      <c r="F7">
+        <v>96.3</v>
+      </c>
+      <c r="G7">
+        <v>72.5</v>
+      </c>
+      <c r="H7">
+        <v>37.590000000000003</v>
+      </c>
+      <c r="I7">
+        <v>56.72</v>
       </c>
     </row>
   </sheetData>
@@ -6184,7 +7405,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126B5B5B-E437-C945-9B34-8DD17CA82909}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -6205,19 +7426,19 @@
         <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>34</v>
@@ -6227,26 +7448,26 @@
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>56.81</v>
       </c>
       <c r="C2">
         <v>48.12</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>59.15</v>
       </c>
       <c r="E2">
-        <v>45.78</v>
+        <v>47.81</v>
       </c>
       <c r="F2">
-        <v>48</v>
+        <v>49.1</v>
       </c>
       <c r="G2">
-        <v>52.73</v>
+        <v>47.18</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6262,17 +7483,17 @@
       <c r="D3">
         <v>39.08</v>
       </c>
-      <c r="E3" s="1">
-        <v>39.659999999999997</v>
-      </c>
-      <c r="F3">
-        <v>38.99</v>
+      <c r="E3">
+        <v>38.96</v>
+      </c>
+      <c r="F3" s="1">
+        <v>39.82</v>
       </c>
       <c r="G3">
-        <v>39.25</v>
+        <v>39.32</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6289,13 +7510,13 @@
         <v>60.81</v>
       </c>
       <c r="E4">
-        <v>60.95</v>
-      </c>
-      <c r="F4">
-        <v>61.06</v>
+        <v>60.73</v>
+      </c>
+      <c r="F4" s="1">
+        <v>60.92</v>
       </c>
       <c r="G4">
-        <v>60.93</v>
+        <v>60.78</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -6314,17 +7535,17 @@
       <c r="D5">
         <v>40.770000000000003</v>
       </c>
-      <c r="E5" s="1">
-        <v>41.41</v>
-      </c>
-      <c r="F5">
-        <v>40.86</v>
+      <c r="E5">
+        <v>40.43</v>
+      </c>
+      <c r="F5" s="1">
+        <v>41.02</v>
       </c>
       <c r="G5">
-        <v>40.659999999999997</v>
+        <v>40.5</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6337,20 +7558,20 @@
       <c r="C6">
         <v>62.84</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>66.8</v>
       </c>
-      <c r="E6">
-        <v>62.92</v>
+      <c r="E6" s="1">
+        <v>67.78</v>
       </c>
       <c r="F6">
-        <v>64.930000000000007</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="G6">
-        <v>64.040000000000006</v>
+        <v>65.28</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6367,16 +7588,16 @@
         <v>49.56</v>
       </c>
       <c r="E7">
-        <v>52.68</v>
-      </c>
-      <c r="F7" s="1">
-        <v>53.18</v>
-      </c>
-      <c r="G7">
-        <v>51.53</v>
+        <v>49.4</v>
+      </c>
+      <c r="F7">
+        <v>53.09</v>
+      </c>
+      <c r="G7" s="1">
+        <v>53.27</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6393,16 +7614,16 @@
         <v>43.63</v>
       </c>
       <c r="E8">
-        <v>44.59</v>
+        <v>44.02</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>44.11</v>
       </c>
       <c r="G8" s="1">
-        <v>45.02</v>
+        <v>44.76</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6419,16 +7640,16 @@
         <v>49.04</v>
       </c>
       <c r="E9">
-        <v>46.97</v>
+        <v>48.18</v>
       </c>
       <c r="F9" s="1">
-        <v>49.74</v>
+        <v>49.32</v>
       </c>
       <c r="G9">
-        <v>48.25</v>
+        <v>48.52</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6444,17 +7665,17 @@
       <c r="D10">
         <v>38.08</v>
       </c>
-      <c r="E10" s="1">
-        <v>40.83</v>
+      <c r="E10">
+        <v>39.81</v>
       </c>
       <c r="F10">
-        <v>38.659999999999997</v>
-      </c>
-      <c r="G10">
-        <v>40.130000000000003</v>
+        <v>40.98</v>
+      </c>
+      <c r="G10" s="1">
+        <v>42.68</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -6467,20 +7688,20 @@
       <c r="C11">
         <v>57.08</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>60.31</v>
       </c>
       <c r="E11">
-        <v>56.52</v>
-      </c>
-      <c r="F11">
-        <v>56.85</v>
+        <v>51.04</v>
+      </c>
+      <c r="F11" s="1">
+        <v>59.25</v>
       </c>
       <c r="G11">
-        <v>54.99</v>
+        <v>58.88</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -6497,16 +7718,16 @@
         <v>42.75</v>
       </c>
       <c r="E12">
-        <v>42.91</v>
+        <v>42.58</v>
       </c>
       <c r="F12" s="1">
-        <v>43.32</v>
+        <v>43.01</v>
       </c>
       <c r="G12">
-        <v>43.06</v>
+        <v>42.76</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6523,16 +7744,16 @@
         <v>63.88</v>
       </c>
       <c r="E13">
-        <v>57.62</v>
-      </c>
-      <c r="F13">
-        <v>59.57</v>
-      </c>
-      <c r="G13" s="1">
-        <v>64.680000000000007</v>
+        <v>67.08</v>
+      </c>
+      <c r="F13" s="1">
+        <v>68.52</v>
+      </c>
+      <c r="G13">
+        <v>63.84</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -6545,71 +7766,19 @@
       <c r="C14">
         <v>44.42</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>53.15</v>
       </c>
       <c r="E14">
-        <v>42.91</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="F14">
-        <v>46.08</v>
+        <v>44.42</v>
       </c>
       <c r="G14">
-        <v>50.97</v>
+        <v>41.62</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="1">
-        <v>44.04</v>
-      </c>
-      <c r="C15">
-        <v>37.79</v>
-      </c>
-      <c r="D15">
-        <v>36.979999999999997</v>
-      </c>
-      <c r="E15">
-        <v>39.5</v>
-      </c>
-      <c r="F15">
-        <v>38.51</v>
-      </c>
-      <c r="G15">
-        <v>37.78</v>
-      </c>
-      <c r="H15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16">
-        <v>48.49</v>
-      </c>
-      <c r="C16">
-        <v>48.67</v>
-      </c>
-      <c r="D16">
-        <v>50.29</v>
-      </c>
-      <c r="E16">
-        <v>48.23</v>
-      </c>
-      <c r="F16">
-        <v>48.91</v>
-      </c>
-      <c r="G16" s="1">
-        <v>49.57</v>
-      </c>
-      <c r="H16" t="s">
         <v>44</v>
       </c>
     </row>
